--- a/artfynd/A 19825-2023 artfynd.xlsx
+++ b/artfynd/A 19825-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 19825-2023 artfynd.xlsx
+++ b/artfynd/A 19825-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>55244948</v>
+        <v>55244724</v>
       </c>
       <c r="B2" t="n">
-        <v>73693</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6440</v>
+        <v>510</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vitgrynig nållav</t>
+          <t>Doftskinn</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Chaenotheca subroscida</t>
+          <t>Cystostereum murrayi</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Eitner) Zahlbr.</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>560766.9739740198</v>
+        <v>561267</v>
       </c>
       <c r="R2" t="n">
-        <v>7024490.831868315</v>
+        <v>7024584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-08-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -787,53 +772,50 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>55244743</v>
+        <v>73128069</v>
       </c>
       <c r="B3" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92522</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1312</v>
+        <v>1179</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Gräddticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Perenniporia subacida</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Peck) Donk</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Sör-Stormyrberget, Ång</t>
+          <t>Sör-stormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>561037.1840131339</v>
+        <v>560803</v>
       </c>
       <c r="R3" t="n">
-        <v>7024543.121393365</v>
+        <v>7024512</v>
       </c>
       <c r="S3" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -860,19 +842,14 @@
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ovanligt substrat</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -881,8 +858,33 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr">
+        <is>
+          <t>mikroskoperad</t>
+        </is>
+      </c>
       <c r="AG3" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ3" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK3" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AM3" t="inlineStr">
+        <is>
+          <t>Trädstam på levande träd</t>
+        </is>
+      </c>
+      <c r="AO3" t="inlineStr">
+        <is>
+          <t>Stem on living tree # Salix caprea</t>
+        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -902,12 +904,7 @@
         <v>55244928</v>
       </c>
       <c r="B4" t="n">
-        <v>89392</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -939,10 +936,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>560909.8774679445</v>
+        <v>560910</v>
       </c>
       <c r="R4" t="n">
-        <v>7024591.903887141</v>
+        <v>7024592</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -972,19 +969,9 @@
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-08-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1011,37 +998,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>55244945</v>
+        <v>55244765</v>
       </c>
       <c r="B5" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>1204</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1051,10 +1033,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>561385.2151288484</v>
+        <v>560983</v>
       </c>
       <c r="R5" t="n">
-        <v>7024594.226383453</v>
+        <v>7024564</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1084,19 +1066,9 @@
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2015-08-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1123,15 +1095,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>55244737</v>
+        <v>55244742</v>
       </c>
       <c r="B6" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1139,21 +1106,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1163,10 +1130,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>560867.0259864134</v>
+        <v>560774</v>
       </c>
       <c r="R6" t="n">
-        <v>7024551.117301362</v>
+        <v>7024497</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1196,19 +1163,9 @@
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2015-08-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1235,15 +1192,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>55244724</v>
+        <v>55244743</v>
       </c>
       <c r="B7" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1251,21 +1203,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>510</v>
+        <v>1312</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftskinn</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cystostereum murrayi</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1275,10 +1227,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>561267.1290797422</v>
+        <v>561037</v>
       </c>
       <c r="R7" t="n">
-        <v>7024583.884689007</v>
+        <v>7024543</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1308,19 +1260,9 @@
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2015-08-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,12 +1292,7 @@
         <v>55244944</v>
       </c>
       <c r="B8" t="n">
-        <v>89356</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1387,10 +1324,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>561258.8689089114</v>
+        <v>561259</v>
       </c>
       <c r="R8" t="n">
-        <v>7024616.064816313</v>
+        <v>7024616</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1420,19 +1357,9 @@
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2015-08-29</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1459,37 +1386,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>55244765</v>
+        <v>55244945</v>
       </c>
       <c r="B9" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1204</v>
+        <v>5447</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1499,10 +1421,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>560982.8150398091</v>
+        <v>561385</v>
       </c>
       <c r="R9" t="n">
-        <v>7024564.095462019</v>
+        <v>7024594</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1532,19 +1454,9 @@
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2015-08-29</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1571,37 +1483,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>55244742</v>
+        <v>55244737</v>
       </c>
       <c r="B10" t="n">
-        <v>81236</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1611,10 +1518,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>560774.0569662871</v>
+        <v>560867</v>
       </c>
       <c r="R10" t="n">
-        <v>7024496.804960875</v>
+        <v>7024551</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1644,19 +1551,9 @@
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2015-08-29</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1683,15 +1580,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>55244842</v>
+        <v>55244948</v>
       </c>
       <c r="B11" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83307</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1699,21 +1591,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6440</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vitgrynig nållav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Chaenotheca subroscida</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Eitner) Zahlbr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1723,10 +1615,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>560796.0858631727</v>
+        <v>560767</v>
       </c>
       <c r="R11" t="n">
-        <v>7024521.027089072</v>
+        <v>7024491</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1756,19 +1648,9 @@
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2015-08-29</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1795,55 +1677,48 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>73128069</v>
+        <v>55244842</v>
       </c>
       <c r="B12" t="n">
-        <v>89967</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>1179</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Gräddticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perenniporia subacida</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Peck) Donk</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sör-stormyrberget, Ång</t>
+          <t>Sör-Stormyrberget, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>560802.9999330696</v>
+        <v>560796</v>
       </c>
       <c r="R12" t="n">
-        <v>7024512.175196659</v>
+        <v>7024521</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1870,59 +1745,19 @@
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2015-08-29</t>
         </is>
       </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Ovanligt substrat</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr">
-        <is>
-          <t>mikroskoperad</t>
-        </is>
-      </c>
       <c r="AG12" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ12" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK12" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>Trädstam på levande träd</t>
-        </is>
-      </c>
-      <c r="AO12" t="inlineStr">
-        <is>
-          <t>Stem on living tree # Salix caprea</t>
-        </is>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
@@ -1936,118 +1771,6 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" t="n">
-        <v>75250140</v>
-      </c>
-      <c r="B13" t="n">
-        <v>89410</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E13" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
-      <c r="P13" t="inlineStr">
-        <is>
-          <t>Sör-stormyrberget, Ång</t>
-        </is>
-      </c>
-      <c r="Q13" t="n">
-        <v>561066.7881185368</v>
-      </c>
-      <c r="R13" t="n">
-        <v>7024429.151081435</v>
-      </c>
-      <c r="S13" t="n">
-        <v>5</v>
-      </c>
-      <c r="T13" t="inlineStr">
-        <is>
-          <t>Västernorrland</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
-        <is>
-          <t>Sollefteå</t>
-        </is>
-      </c>
-      <c r="V13" t="inlineStr">
-        <is>
-          <t>Ångermanland</t>
-        </is>
-      </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>Edsele</t>
-        </is>
-      </c>
-      <c r="Y13" t="inlineStr">
-        <is>
-          <t>2018-10-09</t>
-        </is>
-      </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA13" t="inlineStr">
-        <is>
-          <t>2018-10-09</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT13" t="inlineStr"/>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>Nils Bodin</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>Nils Bodin</t>
-        </is>
-      </c>
-      <c r="AY13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 19825-2023 artfynd.xlsx
+++ b/artfynd/A 19825-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AZ12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55244724</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -898,6 +908,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/73128069</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -995,6 +1010,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55244928</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1092,6 +1112,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55244765</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55244742</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1286,6 +1316,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55244743</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1383,6 +1418,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55244944</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,6 +1520,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55244945</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55244737</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55244948</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1771,8 +1826,26 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/55244842</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>